--- a/artfynd/A 23829-2025 artfynd.xlsx
+++ b/artfynd/A 23829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221007</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>78683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23829-2025 artfynd.xlsx
+++ b/artfynd/A 23829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221007</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23829-2025 artfynd.xlsx
+++ b/artfynd/A 23829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221007</v>
       </c>
       <c r="B2" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23829-2025 artfynd.xlsx
+++ b/artfynd/A 23829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221007</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23829-2025 artfynd.xlsx
+++ b/artfynd/A 23829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221007</v>
       </c>
       <c r="B2" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
